--- a/CBS.FrontDesk.UI/AppFiles/ShareMonthUpload/Processed Data.xlsx
+++ b/CBS.FrontDesk.UI/AppFiles/ShareMonthUpload/Processed Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51D45E41-8086-4F39-91BA-E98F8E305B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA59D6AE-3320-4ACD-82AD-B3ABBC88981F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4B2AE959-C678-4E63-8891-4AF419AB46AC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{4B2AE959-C678-4E63-8891-4AF419AB46AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,17 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="26">
-  <si>
-    <t>BAPCCUL</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
   <si>
     <t xml:space="preserve">Branch Name : </t>
   </si>
   <si>
-    <t>Biyem-Assi</t>
-  </si>
-  <si>
     <t xml:space="preserve">Branch Code : </t>
   </si>
   <si>
@@ -103,13 +97,25 @@
   </si>
   <si>
     <t>December</t>
+  </si>
+  <si>
+    <t>Affiliate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Branch name </t>
+  </si>
+  <si>
+    <t>Branch code</t>
+  </si>
+  <si>
+    <t>Principal Amount</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -128,13 +134,6 @@
     <font>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="5" tint="-0.249977111117893"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -265,13 +264,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -280,23 +282,20 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -611,256 +610,298 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62448346-818D-4C59-85EC-3CAD2561D666}">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.109375" customWidth="1"/>
     <col min="2" max="3" width="29.33203125" customWidth="1"/>
     <col min="4" max="4" width="32" customWidth="1"/>
+    <col min="5" max="5" width="17.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.4">
+      <c r="A1" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="19"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="14"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="7"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B3" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="12"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="7"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="15"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="B4" s="13">
+        <v>46022</v>
+      </c>
+      <c r="C4" s="13"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="9">
-        <v>3</v>
-      </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="15"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="B5" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="10">
-        <v>46022</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="15"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="C5" s="12"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="7"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B6" s="12">
+        <v>10</v>
+      </c>
+      <c r="C6" s="12"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="7"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="15"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="B7" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="9">
-        <v>1000</v>
-      </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="15"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="C7" s="12"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="7"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="17"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B9" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="15"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="16"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="17" t="s">
+      <c r="C9" s="14" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>1</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="18">
+      <c r="B10" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="7">
         <v>10000</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E10" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>2</v>
       </c>
-      <c r="B11" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="18">
+      <c r="B11" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="7">
         <v>15000</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E11" s="7">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>3</v>
       </c>
-      <c r="B12" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="18">
+      <c r="B12" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="7">
         <v>4000</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E12" s="7">
+        <v>560000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>4</v>
       </c>
-      <c r="B13" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="18">
+      <c r="B13" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="7">
         <v>5000</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E13" s="7">
+        <v>740000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>5</v>
       </c>
-      <c r="B14" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="18">
+      <c r="B14" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="7">
         <v>600000</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E14" s="7">
+        <v>78000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>6</v>
       </c>
-      <c r="B15" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="18">
+      <c r="B15" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="7">
         <v>450000</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E15" s="7">
+        <v>67000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>7</v>
       </c>
-      <c r="B16" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="18">
+      <c r="B16" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="7">
         <v>90000</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E16" s="7">
+        <v>890000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>8</v>
       </c>
-      <c r="B17" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="18">
+      <c r="B17" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="7">
         <v>670000</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E17" s="7">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>9</v>
       </c>
-      <c r="B18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" s="18">
+      <c r="B18" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="7">
         <v>34000</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E18" s="7">
+        <v>43000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>10</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="19">
+        <v>23</v>
+      </c>
+      <c r="D19" s="8">
         <v>65000</v>
+      </c>
+      <c r="E19" s="8">
+        <v>23000</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="B7:D7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B6:D6"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>